--- a/tools/excel-oracle/writer-check/spill-shrink.xlsx
+++ b/tools/excel-oracle/writer-check/spill-shrink.xlsx
@@ -1751,7 +1751,7 @@
       </c>
       <c r="B2" s="37">
         <f ca="1">NOW()</f>
-        <v>46305.37694182974</v>
+        <v>46305.40154196236</v>
       </c>
     </row>
   </sheetData>
